--- a/src/dataset/outputs/manifestos.xlsx
+++ b/src/dataset/outputs/manifestos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>index</t>
   </si>
@@ -37,6 +37,12 @@
     <t>Am I sorry? On the one hand, I had a good formal defense because I could argue that E-mail message is not an admissible evidence, since it does not bear the signature of the sender and theoretically could be sent by anybody else who might get access to my computer account or who could very simply falsify the sender's name in the printout. I have even prepared some such examples for the hearing, one of them being a message which I have sent to myself via Universite de Montreal, and another one - a false message from Dr. Swamy which looked like a real thing. Had these arguments been accepted - the case would be thrown out of court. Besides this purely formal defense, I have prepared a substantive defense as well. I sent court orders to come and to testify to three judges involved, Barbeau, Bishop and to former Chief Justice Gold. I would have no difficulty to establish the veracity of my E-mail message by questioning these three judges, and the truth is a good defense in contempt of court cases. (Indeed, when on February 13, 1993, I demanded the case to be heard, the other party withdrew the accusations, and this is the best proof that the accusations were without foundation). My main concern was that the judge would just ignore both defenses. In 1992 I informed Minister of Transport of Canada, Minister of Higher Education of Quebec, MPs Sheila Feinstone and Don Boudria, granting agencies NSERC and FCAR about criminal and unethical activities at Concordia. All of them ignored this information. My experience with the media was even worse. In March of 1992 I have approached a reporter from The Gazette C.Adolph. I showed her all the documents proving fraud and extortion at Concordia University. At the beginning she looked very impressed, made copies of the documents and promised to investigate. All of a sudden, about two weeks later, she left a message on my answering machine to the effect that she found my allegations totally unfounded, that she did not want to talk to me, and should I dare to call her, she would ask the telephone company for protection. I was flabbergasted: if a reporter had some legitimate doubts as to validity of my accusations, she should have discussed them with me, rather than hiding from a discussion in such a ridiculous manner. There is no doubt that her actions were part of the psychiatrist's design: the more shocking and unexpected is the action, the greater is the probability that I explode. When later on, on April 1, 1992, C.Adolph has published in The Gazette an article about me, stating that she found no proof of my allegations, and that it was I harassing everybody else, rather then vice-versa, I had no doubt that she (or her superiors) was bribed. On the other hand, the threat made by Dr. Hogben that the whole hearing was fixed in advance and that "anything can happen in jail", made me very concerned for my life. My own experience with judges strengthened this concern that my life was in danger indeed. It was totally unthinkable for me to accept the "shut-up" money offered by Dr. Hogben on behalf of Concordia administration. I had two reasons to believe that my life, rather then only my freedom, was in danger. First, I had a very serious heart attack in the winter of 1991. A major coronary artery was blocked 100%. I never smoked, did not use any alcohol and was otherwise in excellent physical condition, and this was the reason why I survived. I had no doubt that this heart attack was a result of extreme psychological torture I underwent during the second half of 1990. 1 felt that I was being murdered, very methodically, very professionally and very legally, since there is no such crime in The Criminal Code as deliberate infliction of a heart attack. I underwent an operation of angioplasty and recovered, but I knew that the ballooned arteries have tendency to clog up again. My very serious concern was that should his second heart attack occur in jail, it would be the last one. I suspected that the jail administration paid no attention to the health of prisoners. My present jail experience proved me right. Just this summer a prisoner, 43 years of age, had a heart attack. They kept him in jail for about 6 hours, so that when they have finally delivered him to the hospital, he was already dead. The second grave concern of mine was the vague threat made by Dr. Hogben who said that "anything can happen in jail". From time to time, I have read in the press about highly suspicious deaths at the police stations and in jails. If the former Chief Justice Gold (he was also Concordia Chancellor at that time) could "fix" that I be sentenced to jail, he could also arrange with his police friends and/or Correctional Service friends my “accidental" death. My present jail experience proved me right here as well. The situation was aggravated by the fact that I was 52 at that time, my wife could not provide for the family, and I had two small children: a son, 9 years old, and my daughter was only 7. Despite my first-rate research and teaching record, I was unable to find a job elsewhere though I applied to about 1000 institutions over a number of years not only in Canada or USA, but also in countries as far away as Australia and New Zealand, and I applied not just to universities but also to technical schools and private companies. Taking into consideration that all the legal means seemed to fail, I had no choice but to resort to an illegal way of protection. I decided to take all my guns to the University, to show the guns to one of the conspirators and to tell him that, unless they leave me alone, I would have no choice but to shoot all of them dead. I also took a hammer with me in order to tell them that even if they take my guns away, I would kill them with a hammer, so they better leave me alone. I decided to delay the final decision till Monday, August 24, 1992, to call in the morning the secretary of judge Bishop and to ask her whether she arranged the delay of the hearing. If yes, then everything was fine, nothing was to be done. If no, then to ask whether judge Bishop was coming to testify, and again, if yes, that would be an indication of some respect for the due process, and since I considered my defense perfect, I would be prepared to face the court. If judge Bishop was not coming to court to testify, that would be a clear indication that Dr. Hogben's threats are real. Even in this case I was not yet prepared to execute my plan. I appealed earlier to the university community, asking them to come to the courthouse on August 25. 1 was sure that if many scientists come to support me, no judge would dare to put me in jail. In the morning of August 24, 1992, 1 came to my office and made a phone call to the secretary of judge Bishop. The result was worse than I expected: not only Judge Bishop was not coming, his secretary did not even bother to inform him about the subpoena. It was clear to me that lawlessness ruled in court. I noticed on my desk a copy of the document granting me $1000 in travel expenses for my presentation in Haifa which was scheduled that day, and which I obviously could not make. I took the document and went to the Dean's office and returned it to the budget officer. I noticed that Dean Swamy's door was closed, so I asked the officer if the Dean was in, and she said yes. Usually all the doors at the university were open. I knew from the past experience that whenever some dirty tricks were in the making, Dean Swamy was pretending being scared, hired bodyguards, kept the door of his cabinet locked, etc. (At my trial, Dr. Swamy has admitted that I never threatened him). For me, closed door of Dean Swamy's cabinet was a clear indication that some dirty tricks were in the making again, and I have decided that I had no choice but to implement my plan. I went home, took guns, ammunition and hammer and returned back to the university. I was still very reluctant to implement the plan. I tried once again to check my computer account if there were any support messages coming from colleagues. There were none. Computer still keeps the login time at 1.34 p.m. Since for me Dean Swamy's hiding was an ominous sign, I decided to check again if his door was still closed. I passed through the Dean's office. The door was closed, Swamy was in. At the exit I was stopped by a secretary who asked me to identify myself. I never was stopped before and I did not see anyone else being stopped, so this confirmed to me that the Dean was playing his usual game, telling his secretaries that I wanted to kill him (some secretaries confirmed this at the trial). I have identified myself to the secretary but my feeling of anger has increased. I went to my office to think again whether to proceed with the plan. I was desperately trying to find the reason why not to proceed with my plan but could not find any. I knew that all Canadians are taught that if someone points a gun at you, you should cooperate. Taken this for granted, I could not possibly imagine that my plan might turn into a shooting, but regretfully, it did. Here is how it happened. I phoned Dr. Hogben and invited him to come over to discuss the situation. Dr. Hogben was reluctant to come, but at the end agreed. Almost immediately after that, Dr. MacKay appeared, clearly, he was sent to check my mood and to see whether it would be dangerous for Dr. Hogben to come. The pretext of his arrival was ridiculous: he planned to file some kind of complaint against Dr. Osman, who had no dealings with Dr. MacKay. It was Dr. MacKay who informed me about resignation of Mr. Gervais from his position of the Chair of the Board of Governors of Concordia University. How would he know that, unless Mr. Gervais, who understood the dangerousness of the plot and who was concerned that I might try to kill him, asked Dr. MacKay to inform me about his resignation? I asked Dr. MacKay to come next day to court to testify on my behalf, but Dr. MacKay refused. So, I told him to get out of my office. Probably, Dr. MacKay concluded that it was safe for Dr. Hogben to come. I met Dr. Hogben in the corridor and showed him to the office. I pleaded with Dr. Hogben for about 20 minutes. I told Dr. Hogben that it was Dr. Hogben's duty, as the Union President, to defend me against Administration, that I had a wife and two small children, that I was 52 years old and had no way to provide for my family, should I lose my job, etc. Dr. Hogben could not care less about his duties or about me and my children. He stated again that he negotiated a very good deal for me and that the only alternative is going to court and facing the contempt of court charges and it might end badly. Here I mentioned that I called Palais de Justice, and that I was told that it was another judge Rouleau, not Chaloux, who was assigned to hear the case. This was not a surprise for Dr. Hogben. He explained that judge Chaloux could not be assigned directly to hear the case since he was from the Criminal Division, while the case belonged to the Practice Division. The arrangement, according to Dr. Hogben, was that on the day of hearing judge Rouleau would call in sick, and in the whole courthouse there would be no other judge available but judge Chaloux. How on earth could he possibly know all these details unless someone very qualified has informed him? And who this someone could be but Concordia Chancellor Gold? Even if I had a slightest doubt about the hearing being fixed, they disappeared with this explanation of Dr. Hogben. At this point I decided that I had no choice but to execute my plan. Dr. Hogben in the meantime probably noticed some change in the expression of my face and might have misinterpreted it as fear, because he decided to "go for a kill". He said: "Now you have two options: to go to court or to accept a good deal. Tell me quickly what it would be because I have to go". To this I responded: "Now you have a choice: to be dead or to find a third option, and you tell me quickly what it would be". And with these words I pulled out a revolver and pointed it at Dr. Hogben. I was absolutely sure that Dr. Hogben would choose to cooperate and that I would be able to finally resolve all the problems in a peaceful and satisfactory manner. Regretfully, this did not happen. Although facing a fully loaded revolver (in a revolver bullets are visible), Dr. Hogben did not take it seriously. For some unknown reasons, he was absolutely sure that I under no circumstances would pull the trigger. He said: "This is exactly what we wanted you to do, and now we can put you in jail not for one year but for good". After that he stood up and moved towards the door. And this is where I lost it and started shooting. Dr. Hogben was not surprised at all when he saw the revolver. Someone has prepared him for the situation, and this someone has managed to convince him that there was no way I would shoot. Thus, Dr. Hogben was deliberately and maliciously sacrificed, as were the other victims of shooting, by the conspirators - the university administration: former Chief Justice Gold (who was at that time Concordia Chancellor), Kenniff, Sheinin, Swamy, Osman, and others. End of quotation from previous posting. After reviewing the facts, it is time to pose the question: am I sorry? In order to answer positively, I should determine that there was an alternative way of action. For example, instead of taking my guns and the hammer to the university, to go on August 25 to the court and expect a fair judgment. Was I paranoid to think that Canadian judges are corrupt, have no respect for the law and can render any judgment they please? Here is what I have done to check it. First, I experimented with my own life during criminal proceedings. Authorities did not want me in jail, they wanted me insane. They also wanted to avoid trial, since they knew that former Chief Justice Gold (who was at that time Chancellor of Concordia University) was deeply involved in conspiracy. Lawyer Leclerc, after meeting with Crown, told me that Crown was prepared to accept insanity, without even going to trial, they were also prepared to take the plea of manslaughter. I did not want any of this. I wanted to go to trial, even though I risked to spend the rest of my life in jail. It was more important for me to find out whether I was a crazy murderer, obsessed with paranoia and imagining things, which were just not there, or a reasonable person who acted according to insane circumstances, and did, what anybody else would or should have done. I tested the system thoroughly, whether it respects its own laws. Since I was defending myself, I requested proper conditions to prepare my defense. Remember, officially I was considered innocent, until proven guilty. There was even a precedent: judge Boilard has ordered that one of the accused, who defended himself, was given a trailer, where he could work on his defense. I was refused. There was a fraud with jury selection: it was obvious that the group of people called for jury duty, was not taken at random. I requested access to the records related to jury selection, and judge Martin has refused. I asked him, if he was sure that no fraud was committed, why not let me see the records. And his response was: when something is honest, no proof is necessary! Good argument. I have noticed also that the court clerk did not mix the cards with juror names, but rather placed on top of the hip cards from separate envelope. This is why I, in protest, refused to question the prospected jury. On July 29, 1993, Martin has stopped examination of one very important witness - Swamy, so that I could not help to tell him that he was behaving like little low crook. This is what he said in his judgment that day: I find you guilty of contempt of Court and for that last contempt I sentence you to six months imprisonment to be served consecutively to the sentences which you already served. I can tell you that if an incident such as this morning repeats itself, the same approach will be adopted, and your trial will continue. In passing: policeman, who killed a child by speeding car, got 3 months, policemen, who killed Barnabe, got even less. To call judge a crook is worse than killing a child or beating somebody into a coma. I have decided to test Martin whether he would keep his own word that "if an incident such as this morning repeats itself, the same approach will be adopted, and your trial will continue". So, when he terminated, without any reason, the examination of the next witness, I told him once again, that he was behaving like a crook. He did not keep his word: he closed my defense, without allowing me to testify. In addition, Martin has stopped my address to the jury, which was also illegal. He did it as soon as I stopped reading documents and started discussing the evidence. Accused is not obliged to testify, but when an accused wants to tell his side of the story to the jury, he certainly should be allowed to do so, no matter what his behavior was. For example, there were precedents, where accused had physically attacked jury and/or other witnesses. He got another charge of assault, but his trial continued, as if nothing happened. Judge is dealing with criminals, he should not be sensitive to whatever a criminal says. Nobody should be convicted of the crime he did not commit (in my case I was convicted of premeditated murder, though I certainly did not PLAN to kill anyone), just because he insulted a judge. So, my next test was Court of Appeal, would they have the judicial honesty? The answer is a resounding no. The judgment was written by Proulx. Not only he had no precedent to support his position that accused can exercise his rights only when he is polite, he also wrote an obvious lie, namely, he wrote that provocation is not a defense in the case of murder: he knew very well that Criminal Code considers provocations as a partial defense. The Supreme Court was not any better - it refused to hear my case, without giving any reason, though Supreme Court Act (Sec. 26) states clearly that every judgment should be accompanied by written reason. When I asked why Supreme Court did not give the reason, the Registrar Roland responded that Supreme Court never gives the reason. I wrote then that the fact, that Supreme Court never respected its own law, is not a justification. I asked: if a rapist says that he always raped women, would you accept this as a justification of his actions. They did not like my comparison. So, judges of all levels showed clearly that they have no respect for the law. The next step was to check out judges in civil cases. I have filed several civil lawsuits, where I was absolutely right, in order to see whether I can win any. Here is a short description of what happened in all of them. In April of 1992 1 have filed a lawsuit against Sankar and Swamy for the authorship of my articles. After the shooting, I have been told that civil case can not proceed, until criminal trial is finished. Well, in 1993 the trial was finished, then I was told by judge Lagace that I can not proceed, because the exhibits, which I deposited in 1992, have been mysteriously lost. In order not to waste time, I in the meantime have included two more professors from Concordia (Hoa and Xistris), who were also listed in couple of my articles as co- authors, and whose contribution was also zero. It took several years to achieve. Judges did their best to delay the proceedings. Lawyer Percival-Hilton, who defended Hoa and Xistris, delayed filing defense for almost 2 years, claiming that without exhibits, she could not do it. My argument that her clients had everything they needed in theory possession was ignored by judges: they did their best to support crooks. Each my motion was sent to Associate Chief Justice Deslongchamps for his approval, which introduced additional delay of several months per motion. A good question to ask here, does not Associate Chief Justice have better things to do than to review motions written by convicted murderer Fabrikant? I decided to test the court further: I have filed a motion saying point-blank that Associate Chief Justice is bribed by Defendants, this is why he is delaying the proceedings, and I asked the court to order Associate Chief Justice to stop his illegal activity. Wow, the hell broke loose: now I can not even exercise one of my fundamental rights: to examine Defendants prior to the trial. Judge Journet has refused me this right, without giving any valid reason. I filed an application to the Court of Appeal and was refused even permission to appeal by judge Forget, and I quote the total judgment: Considering that the motion for leave to appeal the judgment rendered on August 11, 2000 by the Hon. Pierre R. Journet of the Superior Court is ill-founded in law, the motion is dismissed, without costs. One does not have to have a law degree to decide whether I was right. Here is a quote from the Code of Civil Procedure of Quebec, Sec. 398: After defense filed, any party may ... summon to be examined before the judge or prothonotary .... any other party .... The word "party" means either Defendant(s) or Plaintiff(s). I knew judges were corrupt and had no respect for the law, but the latest events were astounding even to me: I still hoped that there existed certain limit for their disrespect of the law. I was wrong. Little detail: Journet in his judgment wrote that poor Defendants have already suffered for too long - he had the nerve to reproach to me the Defendants tactics of delays. In 1993, right after the trial, The Gazette had published a totally false article about me claiming that I was a false scientist, knew nothing about Mechanical Engineering, etc. In order to test judicial system, I have filed a libel lawsuit. I have posted separately a long file describing falsity of the article and I shall not repeat it here. Anyone interested can, find it at this web site. I have lost the case. The judge wrote that the article was "well researched". Need I say more? One of my concerns was that a corrupt judge will put me in jail, I might have there yet another heart attack and die due to denial of medical care. In a way, this scenario did take place: I had a heart attack while in jail in May of 1998. I survived it not because I got proper medical care, but just I was lucky that the heart attack was not deadly, probably, due to the fact that I never smoked, my blood pressure and cholesterol are normal, etc. With several hours of delay, jailers finally brought me to Saint-Francois Hospital in Quebec-City. This hospital is not equipped to perform either angioplasty or bypass surgery. So, if a serious complication took place, I would have died there. Now I give a brief explanation of some terminology used. Angiography is a test of the status of coronary arteries. A catheter is inserted through a vein in the leg up to the heart. Some ink is injected from that catheter into the bloodstream of coronary arteries, and simultaneously, X-ray film is being shot, thus giving a clear picture of coronary arteries of working heart in motion. Angioplasty is a procedure of opening up of clogged coronary arteries. A catheter, containing a small balloon, is inserted in a leg vein and moved up to the clogged coronary artery, the balloon is inflated thus opening the artery, and that's it. The whole operation takes less than an hour, and the next day the patient goes home. Bypass surgery is a very complicated and serious operation. The patient's chest is cut open, the heart is stopped, and the patient is attached to the heart-lungs machine. A vein is taken from the patient's leg and one end of that vein is sawn to aorta, while the other end is sawn to the clogged artery, thus by-passing the clogged place. Many things can go wrong during such a complicated operation, and even if everything is fine, the recovery time is about 30 days. The doctor at St-Francois hospital did his best to kill me passively: he did not offer me the blood-clot baster, which needs to be applied within 3 hours after a heart attack, though I requested it. His response was that he was not sure I had a heart attack. Twelve hours later, when the medical Mafiosi saw that I did not die, they finally used this blood-clot baster, which was too late: the harm to my heart has been done. From day one, I demanded angiography and angioplasty to be done. Instead, cardiologist Couture connected me to several IV pumping into me various medications. These IV were defective, since they carried a lot of air bubbles, so I had to be vigilant and shake the tube whenever I saw next bubble. Usually, intravenous machine signals alarm, when air bubble comes to patient. My machines did not: I suspect that alarm was deliberately disconnected. The purpose was obvious: sufficient amount of air pumped into my veins can kill, with no trace of fowl play. When I got hold of my medical file, I saw a lab test of my blood, indicating that Couture deliberately used the dosage of Heparine either too much or too low to have a beneficial effect. Heparine inhibits blood coagulation thus preventing blood clots, but too much Heparine can result in brain hemorrhage, and this is what Couture hoped for. For example, on May 9, 1998 at 3 p.m., my blood test showed the coagulation time 240 seconds, while normal value (without Heparine) is between 26 and 32 seconds; the therapeutic zone is 63-114 seconds. Couture overmedicated me more than double. This can not be an honest mistake. The blood test on the same date at 10.45 p.m. gave my coagulation time at 44.7 seconds, which is too low for any therapeutic effect. Couture deliberately jumped between overmedicating me to undermedicating, hoping to trigger a disastrous reaction. He did not succeed, because I ordered to be disconnected from all IV needles. After this was done, I immediately felt myself better. When Couture learned about my refusal to accept IV, he called a psychiatrist to evaluate whether I am mentally fit to make the decisions about my health care. He wanted to declare me mentally inapt, so the he could kill me by his “treatment" against my will. I was smart enough to refuse to speak with his psychiatrist, because if I did speak with her, no matter what I would say, she could write that she examined me and that I was mentally inapt. Since I did not speak with her, she could not come to any conclusion about me, and this saved me. As soon as Couture learned about his defeat, he changed his mind and told me that he had arranged for an angiography and angioplasty on May 15, 1998, exactly as I demanded from the very beginning. Several months later, I have heard of a young boy, killed in Montreal hospital - they just pumped too much liquid in his body. I just might have saved my life by pulling those needles out. On May 15, 1998, Dr. Barbeau has performed an angiography, but refused to do angioplasty, saying that it was "too difficult". He suggested by-pass surgery, and even made an appointment for me on the next working day - May 19, 1998. It looked strange to me: they certainly had a waiting list, why would they allow a convicted murderer to jump the queue? I would have understood, if they had told me that I was to die next day, if I had not done the bypass surgery, but this was not the case. Besides, they could not explain to me, why angioplasty was not possible. Since I did not feel that I was about to die, I decided to take some time and to ask for second opinion. I have sent my angiography film to several Montreal hospitals. The result was surprising: all doctors claimed that angioplasty was too dangerous (not just difficult, as Barbeau said), and that I should opt for bypass surgery. None though could explain why would the angioplasty be dangerous. So, I decided to make an experiment. I asked my wife to send a copy of the angiography film to several doctors in US, using her name, rather than mine. As I expected, all the US doctors were unanimous: angioplasty was possible, and each was prepared to do it. My next step - to show these opinions to Quebec doctors and ask them why their opinion was so different from that of US colleagues. None agreed to comment on these opinions. I had opinions from such respectable places as Harvard Medical School, New York University and Columbia University. My next step - since all those recommending by-pass surgery were not surgeons themselves, I requested an appointment with a cardiac surgeon to discuss possible by-pass. I had such an appointment in November of 1998 with surgeon C. Pelletier at the Montreal Heart Institute. He told me that two arteries - Circumflex and Marginal were non-operable, while two others LAD and Diagonal were operable. He did not explain why, and he refused to discuss the option of angioplasty. A funny thing happened in 2000: I got an opinion of yet another cardiac surgeon Teijiera (Sherbrooke). He also did not recommend bypass surgery though for reasons totally opposite to those of Pelletier. According to Teijiera, Circumflex and Marginal were operable, while the other 2 were not. There was one specialist from BC, who also agreed to do angioplasty. Jailers wanted me dead, so they refused to bring me to British Columbia for angioplasty, though some of my colleagues and relatives were prepared to pay all the related expenses. Based on false statements of Quebec medical Mafiosi, jailers declared that I was getting the best treatment available and that all I needed was available in Quebec. I decided to check once again our judiciary. I filed several motions in Federal Court explaining that my life was in danger, that my heart was deteriorating and that I needed to be transported to British Columbia for angioplasty. Judge of Federal Court McGillis has declared me vexatious pleader and has forbidden me to file any action in Federal Court. I moved to Quebec Superior Court. I filed an action for damages against jail doctor Corbin and a motion asking court to order jailers to bring me to BC for an angioplasty. My action was dismissed even without hearing and judge of Superior Court Rolland has declared me also a vexatious pleader and now I was forbidden to file any action in Superior Court. Jailers knew that shooting in Concordia took place because I felt my life to be in danger and that the courts were corrupt and would not protect my life. Now they created exactly the same situation: my life was again in danger and both Federal and Superior Court judges demonstrated themselves as totally corrupt. Jailers hoped that they once again would be able to provoke me into a violent reaction. They failed: I never even raised my voice at anyone; I never begged for my life, but I demanded treatment and I filed numerous complaints. My next step was to file complaints against jail doctors and nurses with their respective Discipline Committee. I was not going to let them kill me quietly. One such complaint was considered against jail doctor Corbin and the Discipline Committee has decided that my complaint was totally without merit, that I was getting the best treatment possible. Of course, Corbin found 2 other doctors to testify as experts that this indeed was the case. Mafiosi are one family, supporting each other in any crime. In the meantime, my heart continued to deteriorate. Quebec doctors were ready to help government to kill me, but they did not want to be bothered by my complaints, so they demanded government to forbid me filing complaints; government was happy to oblige. In June of 2001, Attorney General of Canada on behalf of Solicitor General of Canada went to court against me asking the judge to forbid me filing complaints against doctors, nurses and lawyers. Judge Durand was also happy to oblige: he immediately issued an order stopping all complaints already filed and forbidding me to file new ones. Now I was silenced completely. Jailers hoped that this would provoke me, they were wrong again. I passed the provocation school at Concordia, I am immune now to any provocation. I have written a separate posting about these proceedings if anyone wants more details. A new test was done on July 4, 2001, and it showed that my angina has spread over the heart, so that even corrupt Quebec cardiologist Ayas had to write that my life was "possibly" in danger, but still he deliberately lost months by writing letters to Montreal Heart Institute and Jewish General Hospital, thus giving jailers excuse not to bring me to BC since they were waiting for response from these places. In December of 2001, jailers finally have transferred me to BC and on January 7, 2002, 1 had finally angioplasty done. One of the 4 blocked arteries in the left side was o</t>
   </si>
   <si>
+    <t>2083  A  European  Declaration  of  Independence  De  Laudt  Novae  Militiae  Pauperes  commiliumes  Christi  Templique  Solomonid  By  Andrew  Berwick,  London  -  2011  About  the  compendium  -  2083  "The  men  the  European  public  admires  most  extravagantly  are  the  most  daring  liars;  the  men  they  detest  most  violently  are  those  who  try  to  tell  them  the  truth."  You  can  see  a  movie  presentation  of  the  compendium  by  visiting  the  below  links.  It  will  not  be  available  for  a  long  period  so  consider  taking  a  backup  copy  of  it:  http://www.youtube.com/watch?v=vQOfH8Djlmw  http://www.veoh.com/watch/v21123164bZCBQeZ8  After  years  of  work  the  first  edition  of  the  compendium  "2083  -  A  European  Declaration  of  Independence"  is  completed.  If  you  have  received  this  book,  you  are  either  one  of  my  former  7000  patriotic  Facebook  friends  or  you  are  the  friend  of  one  of  my  FB  friends.  If  you  are  concerned  about  the  future  of  Western  Europe  you  will  definitely  find  the  information  both  interesting  and  highly  relevant.  I  have  spent  several  years  writing,  researching  and  compiling  the  information  and  I  have  spent  most  of  my  hard  earned  funds  in  this  process  (in  excess  of  300  000  Euros).  I  do  not  want  any  compensation  for  it  as  it  is  a  gift  to  you,  as  a  fellow  patriot.  Much  of  the  information  presented  in  this  compendium  (3  books)  has  been  deliberately  kept  away  from  the  European  peoples  by  our  governments  and  the  politically  correct  mainstream  media  (MSM).    More  than  90%  of  the  EU  and  national  parliamentarians  and  more  than  95%  of  journalists  are  supporters  of  European  multiculturalism  and  therefore  supporters  of  the  ongoing  Islamic  colonisation  of  Europe;  yet,  they  DO  NOT  have  the  permission  of  the  European  peoples  to  implement  these  doctrines.  The  compendium,  -  "2083  -  A  European  Declaration  of  Independence"  -  documents  through  more  than  1000  pages  that  the  fear  of  Islamisation  is  all  but  irrational.  It  covers  the  following  main  topics:  1.  The  rise  of  cultural  Marxism/multiculturalism  in  Western  Europe  2.  Why  the  Islamic  colonization  and  Islamisation  of  Western  Europe  began  3.  The  current  state  of  the  Western  European  Resistance  Movements  (anti-Marxist/anti-Jihad  movements)  4.  Solutions  for  Western  Europe  and  how  we,  the  resistance,  should  move  forward  in  the  coming  decades  5.  +  Covering  all,  highly  relevant  topics  including  solutions  and  strategies  for  all  of  the  8  different  political  fronts  The  compendium/book  presents  advanced  ideological,  practical,  tactical,  organisational  and  rhetorical  solutions  and  strategies  for  all  patriotic-minded  individuals/movements.  The  book  will  be  of  great  interest  to  you  whether  you  are  a  moderate  or  a  more  dedicated  cultural  conservative/nationalist.  Included  are  also  demographical  studies,  historical  statistics,  forecasts  and  insights  on  various  subjects  related  to  the  ongoing  and  future  struggle  of  Europe.  It  covers  most  topics  related  to  historical  events  and  aspects  of  past  and  current  Islamic  Imperialism,  which  is  now  removed  or  falsified  by  our  academia  by  instruction  of  Western  Europe's  cultural  relativist  elites  (cultural  relativism=cultural  Marxism).  It  offers  thorough  analysis  of  Islam,  which  is  unknown  to  a  majority  of  Europeans.  It  documents  how  the  political  doctrines  known  as  multiculturalism/cultural  Marxism/cultural  relativism  was  created  and  implemented.  Multiculturalists/cultural  Marxists  usually  operate  under  the  disguise  of  humanism.  A  majority  are  anti-nationalists  and  want  to  deconstruct  European  identity,  traditions,  culture  and  even  nation  states.  As  we  all  know,  the  root  of  Europe's  problems  is  the  lack  of  cultural  self-confidence  (nationalism).  Most  people  are  still  terrified  of  nationalistic  political  doctrines  thinking  that  if  we  ever  embrace  these  principles  again,  new  "Hitler's"  will  suddenly  pop  up  and  initiate  global  Armageddon...  Needless  to  say;  the  growing  numbers  of  nationalists  in  W.  Europe  are  systematically  being  ridiculed,  silenced  and  persecuted  by  the  current  cultural  Marxist/multiculturalist  political  establishments.  This  has  been  a  continuous  ongoing  process  which  started  in  1945.  This  irrational  fear  of  nationalistic  doctrines  is  preventing  us  from  stopping  our  own  national/cultural  suicide  as  the  Islamic  colonization  is  increasing  annually.  This  book  presents  the  only  solutions  to  our  current  problems.  You  cannot  defeat  Islamisation  or  halt/reverse  the  Islamic  colonization  of  Western  Europe  without  first  removing  the  political  doctrines  manifested  through  multiculturalism/cultural  Marxism...  I  have  written  approximately  half  of  the  compendium  myself.  The  rest  is  a  compilation  of  works  from  several  courageous  individuals  throughout  the  world.  I  originally  planned  to  add  a  database  of  high  quality  graphic  illustrations  and  pictures.  However,  the  document  (file)  would  have  been  un-practically  large  which  would  complicate  the  process  of  efficient  distribution.  Distribution  of  the  book  The  content  of  the  compendium  truly  belongs  to  everyone  and  is  free  to  be  distributed  in  any  way  or  form.  In  fact,  I  ask  only  one  favour  of  you;  I  ask  that  you  distribute  this  book  to  everyone  you  know.  Please  do  not  think  that  others  will  take  care  of  it.  Sorry  to  be  blunt,  but  it  does  not  work  out  that  way.  If  we,  the  Western  European  Resistance,  fail  or  become  apathetic,  then  Western  Europe  will  fall,  and  your  freedom  and  our  children's  freedom  with  it...    It  is  essential  and  very  important  that  everyone  is  at  least  presented  with  the  truth  before  our  systems  come  crashing  down  within  2  to  7  decades.  So  again,  I  humbly  ask  you  to  re-distribute  the  book  to  as  many  patriotic  minded  individuals  as  you  can.  I  am  100%  certain  that  the  distribution  of  this  compendium  to  a  large  portion  of  European  patriots  will  contribute  to  ensure  our  victory  in  the  end.  Because  within  these  three  books  lies  the  tools  required  to  win  the  ongoing  Western  European  cultural  war.  As  already  mentioned;  the  compendium  is  a  compilation  of  works  from  multiple  courageous  individuals  throughout  the  world.  I  have  spent  more  than  three  years  writing  and/or  compiling  most  of  the  content.  None  of  the  other  authors  have  been  asked  to  participate  in  this  project  due  to  practical  and  security  reasons  but  most  of  them  have  made  their  material  available  for  distribution.  The  needs  of  the  many  outweigh  the  needs  of  the  few.  This  is  the  reason  why  I  have  decided  to  allow  the  content  of  this  compendium  to  be  freely  redistributed  and  translated.  Consider  it  my  personal  gift  and  contribution  to  all  Europeans.  The  sources  are  not  embedded  into  the  document  for  this  reason  (easier  to  use  and  distribute  the  various  articles).  However,  it  is  required  that  the  author(s)  are  credited  when  the  material  is  used.  As  such,  the  intellectual  property  of  this  compendium  belongs  to  all  Europeans  across  the  European  world  and  can  be  distributed  and  translated  without  limitations.  Efficient  distribution  and  circulation  will  be  possible  if  those  who  agree  with  at  least  some  of  its  content,  principles  or  ideas  contribute  to  spread  the  information.  If  you  are  reading  this  you  will  know  that  many  people  will  be  interested  in  obtaining  the  compendium  (3  books).  Let's  use  this  momentum  to  our  advantage  as  it  will  surely  benefit  our  struggle.  I'm  depending  on  you  to  distribute  the  book  or  some/all  of  its  content  to  as  many  patriotic  European  political  activists  as  possible.  Let  them  know  what  is  going  on  and  what  is  required  of  each  and  every  one  of  us.  After  all,  we  do  not  only  have  a  right  to  resist  the  current  development,  it  is  our  duty  as  Europeans  to  prevent  the  annihilation  of  our  identities,  our  cultures  and  traditions  and  our  nation  states!  Please  contribute  to  distribute  the  compendium  to  as  many  patriotic  minded  Europeans  as  humanly  possible  in  all  26  European  countries.  This  is  only  be  the  beginning...!  By  including  the  "legal  disclaimer"  in  "Book  3;  "will  allow  everyone  to  distribute  the  content  without  violating  any  European  laws.  If  you  are  still  in  doubt  feel  free  to  delete  or  change  the  wording  in  certain  chapters  before  distribution.  Please  help  to  make  this  book  available  through  various  torrents,  blogs,  websites,  on  Facebook,  on  Twitter,  on  forums  and  through  other  arenas.  It  is  truly  a  one-of-a-kind,  unique  and  great  tool  that  can  and  should  be  used  by  all  cultural  conservatives  in  the  decades  to  come.  Priority  objective  -  translating  the  book  to  German,  French  and  Spanish.  I  highly  recommend  that  especially  a  French,  German  and  Spanish  patriot  takes  responsibility  and  ensures  that  this  compendium  is  either  distributed  and/or  translated  to  your  respective  language.  It  should  be  distributed  to  torrents,  websites,  Facebook  groups  and  other  political  groups  where  there  are  high  concentrations  of  cultural  conservatives/nationalists/patriots.  I  have  been  unsuccessful  to  efficiently  distribute  the  compendium  to  especially  French,  German  and  Spanish  speaking  individuals  due  to  language  barriers.  It  is  therefore  essential  that  someone  steps  up  and  takes  responsibility  to  distribute  it  to  as  many  as  humanly  possible.  If  you,  yourself,  are  too  busy,  unavailable  or  unable  to  contribute  to  help  translate  it,  please  do  contact  one  of  many  cultural  conservative/nationalist  intellectuals/writers/journalists  in  your  country.  Contact  individuals  you  know  who  are  not  afraid  to  operate  outside  the  boundaries  of  political  correctness.  We,  the  right  wing  Resistance  Movements  of  Europe  depend  on  efficient  re-  distribution of  this  vital  information  included  in  this  compendium.  The  efficient  distribution  of  this  book  to  all  nationalists  of  Europe  may  significantly  contribute  to  future  regime  shifts.  Because  within  this  compendium  lies  the  tools  and  knowledge  on  exactly  how  to  replace  our  current  regimes.  I  really  hope  someone  will  accept  this  very  important  task  and  contribute;  because  if  you  won't,  no  one  will...  Extracting  info  from  the  document  or  convert  from  a  Word  file  to  a  PDF  file   +  translation  service  It's  easy  to  convert  the  document  from  a  Word  file  to  a  PDF  file  or  any  other  format  providing  you  have  the  Microsoft  Word/Office  software  (preferably  Word  2007  or  newer).  If  you  do  not  have  this  software  you  can  either  download  the  free  "Word  Viewer"  which  allows  you  to  view,  print  and  copy  Word  documents,  even  if  you  don't  have  Word  installed.  Just  do  a  search  for  the  key  word  "Word  Viewer"  at  the  following  site:  http://www.microsoft.com/downioads  or  use  the  following  direct  download  link:  http  ://www.  microsoft,  com/downloads/details.  aspx?display  la  ng=en&amp;FamilyID=3657ce88-7cfa-457a-9aec-f4f827f20cac  You  can  also  just  buy  the  full  Office  package  or  download  a  free  trial  from  the  Microsoft  site:  http://office.microsoft.com  or  alternatively,  go  to  one  of  the  following  torrent  sites  to  download  it  for  free:  Lthepiratebay.org  3.  torrentreactor.net         5.  torrentz.com  2.  btscene.com  4.  extratorrent.com  6.  btmon.com  You  must  first  download  a  torrent  application.  The  best  torrent  application  (uTorrent)  can  be  downloaded  here:  www.utorrent.com  If  you  want  Word  2007  for  longer  than  the  60  day  trial  it  is  likely  you  will  have  to  download  a  serial  code  which  allows  you  to  unlock  the  software  permanently  or  at  least  extend  the  trial  period  for  6-12  months.  I  chose  to  send  the  compendium  as  a  Word  file  for  the  following  reason:  1 .  MS  Word  is  one  of  the  most  common  and  popular  software  formats  2.  Significantly  easier  to  edit  the  document  compared  to  PDF  3.  A  Word  file  is  significantly  smaller  than  a  PDF  file  (3,5  MB  vs  8-10  MB)  4.  The  quality  of  the  images  are  conserved  a  lot  better  than  in  a  PDF  5.  Distribution:  it  is  easier  to  avoid  spam  filters  with  a  file  smaller  than  5  MB  Since  I  have  chosen  to  send  the  document  in  Word  format  you  can  easily  extract  all  information  and  the  images  from  the  Word  file.  I  deliberately  avoided  locking  the  document  for  this  reason.  If  you  want  to  extract  the  images  from  word  you  can  do  the  following:  1.     Simply  open  MS  Paint  (standard  Windows  program),  copy  the  image  from  Word  and  paste  it  in  Paint.  You  then  save  the  image  in  Paint  as  a  jpg  or  any  other  format.  It  is  easy  to  convert  the  file,  if  desired,  to  a  PDF  file  or  any  other  format.  Simply  save  the  Word  file  as  a  PDF  file.  As  for  extraction  from  a  PDF  file;  several  software  programs  including  newer  versions  of  Adobe  Acrobat  allow  conversion  and  extraction.  Just  google  the  word;  "PDF  to  Word  converter"  or  download  the  following  free  converter  software:  http://www.hellopdf.com/download.php  As  for  a  free  and  powerful  translator  service;  the  google  translation  service  offers  a  powerful  and  relatively  accurate  tool:  http://transiate.googie.com  Display  using  kindle/nook/iPad  Kindle,  nook  or  iPad  is  a  hardware  platform  (LCD  board)  very  suitable  for  reading  e-  books  and  other  digital  media.  It  costs  as  little  as  100-200  USD  on  the  second  hand  market.  Also,  there  are  other  hand  held  devices  like  iPhone.  All  you  have  to  do  is  select  Word  as  input  and  kindle/nook/iPad/iPhone  as  output  and  transfer  the  file.  Converting  the  Word  file  to  paper  Successful  self-publishers  today  leverage  the  benefits  provided  by  print-on-demand  services,  where  they  don't  need  to  waste  money  on  printing  costs  or  on  inventory  and  stocking  fees.  A  "print-on-demand"  (POD)  service,  sometimes  called  publish-on-demand,  is  a  printing  technology  and  business  process  in  which  new  copies  of  a  book  are  not  printed  until  an  order  has  been  received.  Many  traditional  small  presses  have  replaced  their  traditional  printing  equipment  with  POD  equipment  or  contract  their  printing  out  to  POD  providers.  When  customers  order  their  books,  self-publishing  outlets  like  Cafepress.com  and  others  (see  list)  will  print  on-demand  as  many  book  as  needed  and  they  will  also  ship  them  and  get  payments  for  them  from  those  ordering.  These  self-publishing  services  accept  uploaded  digital  content  such  as  Word  or  PDF  files.  However,  due  to  the  controversial  nature  of  the  content  of  this  book,  the  individual  that  makes  the  initial  arrangement  has  to  be  careful  and  may  need  to  cut  away  certain  chapters  before  using  commercial  services  such  as  these.  Self  publishing  services/books  on  demand  services:  lulu.com  xlibris.com  authorhouse.co.uk  unibook.com  createspace.com  webook.com  spirepublishing.com  createbooks.com  cafepress.co.uk  selfpublishing.com  trafford.com  booksurge.com  booksondemand.com  infinitypublishing.com  lightningsource.com  blurb.com  Guide  to  self  publishing:  http://www.masternewmedia.org/self-publish-your-book-guide-to-the-best-self-publishing-services/  Intro  to  e-book  format:  http://toc.oreilly.com/2008/04/ebook-format-primer.html  Sacrifices  made  when  creating  the  compendium  I've  spent  a  total  of  9  years  of  my  life  working  on  this  project.  The  first  five  years  were  spent  studying  and  creating  a  financial  base,  and  the  last  three  years  was  spent  working  full  time  with  research,  compilation  and  writing.  Creating  this  compendium  has  personally  cost  me  a  total  of  317  000  Euros  (130  000  Euros  spent  from  my  own  pocket  and  187  500  Euros  for  loss  of  income  during  three  years).  All  that,  however,  is  barely  noticeable  compared  to  the  sacrifices  made  in  relation  to  the  distribution  of  this  book,  the  actual  marketing  operation;)  The  importance  of  spreading  the  truth  and  distribute  sound  strategies  cannot  be  underestimated  as  it  is  at  the  very  core  of  our  current  resistance  efforts.  I  do  hope  you  take  the  time  to  read  it.  Several  aspects  of  the  work  is  truly  unique  and  no  similar  compendium  exists  today.  Don't  let  the  topics  discussed  in  the  books  startle  you  too  much.  Many  of  the  topics  may  seem  completely  absurd  or  too  radical  today,  but  in  a  couple  of  decades,  you  will  start  to  understand  its  relevancy  to  our  struggle.  Nevertheless,  if  the  content  freaks  you  out  too  much,  to  a  degree  where  you  want  to  delete  it,  I  would  highly  recommend  you  rather  save  it  on  a  USB  flash  drive  (small  memory  chip)  and  place  the  chip  in  a  safe  location.  Because  it  is  likely  that  you  will  want  to  read  it  at  some  point  in  time.  After  all,  we  can  only  ignore  central  aspects  of  reality  for  so  long.  A  message  from  the  author/creator  of  the  compendium  I  hope  you  enjoy  this  compendium.  It  currently  offers  the  most  comprehensive  database  of  solution  oriented  subjects.  As  mentioned,  I  only  ask  one  thing  from  you;  that  you  distribute  this  book  to  your  friends  and  ask  them  to  forward  it  to  "their"  friends,  especially  to  individuals  who  have  a  patriotic  mindset.  Please  help  us  and  help  yourself,  your  family  and  friends  by  contributing  to  spread  the  tools  which  will  ensure  our  victory;  for  the  truth  must  be  known...  It  is  not  only  our  right  but  also  our  duty  to  contribute  to  preserve  our  identity,  our  culture  and  our  national  sovereignty  by  preventing  the  ongoing  Islamisation.  There  is  no  Resistance  Movement  if  individuals  like  us  refuse  to  contribute...  Multiculturalism  (cultural  Marxism/political  correctness),  as  you  might  know,  is  the  root  cause  of  the  ongoing  Islamisation  of  Europe  which  has  resulted  in  the  ongoing  Islamic  colonisation  of  Europe  through  demographic  warfare  (facilitated  by  our  own  leaders).  This  compendium  presents  the  solutions  and  explains  exactly  what  is  required  of  each  and  every  one  of  us  in  the  coming  decades.  Everyone  can  and  should  contribute  in  one  way  or  the  other;  it's  just  a  matter  of  will.  Time  is  of  the  essence.  We  have  only  a  few  decades  to  consolidate  a  sufficient  level  of  resistance  before  our  major  cities  are  completely  demographically  overwhelmed  by  Muslims.  Ensuring  the  successful  distribution  of  this  compendium  to  as  many  Europeans  as  humanly  possible  will  significantly  contribute  to  our  success.  It  may  be  the  only  way  to  avoid  our  present  and  future  dhimmitude  (enslavement)  under  Islamic  majority  rule  in  our  own  countries.  I  have  been  unable  to  send  this  compendium  to  many  people,  for  various  reasons,  so  I  truly  hope  you  will  be  willing  to  contribute.  It  should  be  noted  that  English  is  my  secondary  language  and  due  to  certain  security  precautions  I  was  unable  to  have  the  documents  professionally  edited  and  proof  read.  Needless  to  say,  there  is  a  potential  for  improving  it  literarily.  As  such,  consider  it  a  "first  edition  draft".  The  responsibility  falls  upon  you  now  as  I  will,  for  obvious  reasons,  not  be  able  to  develop  it  any  further.  Any  and  all  individuals  with  the  appropriate  skills  are  encouraged  to  contribute  to  a  second  edition  of  this  compendium  by  improving  and  expanding  it  where  needed.  Sincere  and  patriotic  regards,  Andrew  Berwick,  London,  England  -  2011  Justiciar  Knight  Commander  for  Knights  Templar  Europe  and  one  of  several  leaders  of  the  National  and  pan-European  Patriotic  Resistance  Movement  With  the  assistance  from  brothers  and  sisters  in  England,  France,  Germany,  Sweden,  Austria,  Italy,  Spain,  Finland,  Belgium,  the  Netherlands,  Denmark,  the  US  etc.  Introduction  to  the  compendium  -  "2083'  The  introductory  chapter  explains  how  "cultural"  Marxism  gradually  infiltrated  our  post-  WW2  societies.  It  is  essential  to  understand  how  it  started  in  order  to  comprehend  our  current  issues.  The  chapter  was  written  for  the  US  specifically  but  applies  to  Western  Europe  as  well.  Introduction  -  What  is  "Political  Correctness"?  One  of  conservatism's  most  important  insights  is  that  all  ideologies  are  wrong.  Ideology  takes  an  intellectual  system,  a  product  of  one  or  more  philosophers,  and  says,  "This  system  must  be  true."  Inevitably,  reality  ends  up  contradicting  the  system,  usually  on  a  growing  number  of  points.  But  the  ideology,  by  its  nature,  cannot  adjust  to  reality;  to  do  so  would  be  to  abandon  the  system.  Therefore,  reality  must  be  suppressed.  If  the  ideology  has  power,  it  uses  its  power  to  undertake  this  suppression.  It  forbids  writing  or  speaking  certain  facts.  Its  goal  is  to  prevent  not  only  expression  of  thoughts  that  contradict  what  "must  be  true,"  but  thinking  such  thoughts.  In  the  end,  the  result  is  inevitably  the  concentration  camp,  the  gulag  and  the  grave.  But  what  happens  today  to  Europeans  who  suggest  that  there  are  differences  among  ethnic  groups,  or  that  the  traditional  social  roles  of  men  and  women  reflect  their  different  natures,  or  that  homosexuality  is  morally  wrong?  If  they  are  public  figures,  they  must  grovel  in  the  dirt  in  endless,  canting  apologies.  If  they  are  university  students,  they  face  star  chamber  courts  and  possible  expulsion.  If  they  are  employees  of  private  corporations,  they  may  face  loss  of  their  jobs.  What  was  their  crime?  Contradicting  the  new  EUSSR  ideology  of  "Political  Correctness."  But  what  exactly  is  "Political  Correctness?"  Marxists  have  used  the  term  for  at  least  80  years,  as  a  broad  synonym  for  "the  General  Line  of  the  Party."  It  could  be  said  that  Political  Correctness  is  the  General  Line  of  the  Establishment  in  Western  European  countries  today;  certainly,  no  one  who  dares  contradict  it  can  be  a  member  of  that  Establishment.  But  that  still  does  not  tell  us  what  it  really  is.  We  must  seek  to  answer  that  question.  The  only  way  any  ideology  can  be  understood,  is  by  looking  at  its  historical  origins,  its  method  of  analysis  and  several  key  components,  including  its  place  in  higher  education  and  its  ties  with  the  Feminist  movement.  If  we  expect  to  prevail  and  restore  our  countries  to  full  freedom  of  thought  and  expression,  we  need  to  know  our  enemy.  We  need  to  understand  what  Political  Correctness  really  is.  As  you  will  soon  see,  if  we  can  expose  the  true  origins  and  nature  of  Political  Correctness,  we  will  have  taken  a  giant  step  toward  its  overthrow.  How  it  all  began  -  Political  Correctness  is  Cultural  Marxism  Most  Europeans  look  back  on  the  1950s  as  a  good  time.  Our  homes  were  safe,  to  the  point  where  many  people  did  not  bother  to  lock  their  doors.  Public  schools  were  generally  excellent,  and  their  problems  were  things  like  talking  in  class  and  running  in  the  halls.  Most  men  treated  women  like  ladies,  and  most  ladies  devoted  their  time  and  effort  to  making  good  homes,  rearing  their  children  well  and  helping  their  communities  through  volunteer  work.  Children  grew  up  in  two-parent  households,  and  the  mother  was  there  to  meet  the  child  when  he  came  home  from  school.  Entertainment  was  something  the  whole  family  could  enjoy.  What  happened?  If  a  man  of  the  1950s  were  suddenly  introduced  into  Western  Europe  in  the  2000s,  he  would  hardly  recognise  it  as  the  same  country.  He  would  be  in  immediate  danger  of  getting  mugged,  carjacked  or  worse,  because  he  would  not  have  learned  to  live  in  constant  fear.  He  would  not  know  that  he  shouldn't  go  into  certain  parts  of  the  city,  that  his  car  must  not  only  be  locked  but  equipped  with  an  alarm,  that  he  dare  not  go  to  sleep  at  night  without  locking  the  windows  and  bolting  the  doors  -  and  setting  the  electronic  security  system.  If  he  brought  his  family  with  him,  he  and  his  wife  would  probably  cheerfully  pack  their  children  off  to  the  nearest  public  school.  When  the  children  came  home  in  the  afternoon  and  told  them  they  had  to  go  through  a  metal  detector  to  get  in  the  building,  had  been  given  some  funny  white  powder  by  another  kid  and  learned  that  homosexuality  is  normal  and  good,  the  parents  would  be  uncomprehending.  In  the  office,  the  man  might  light  up  a  cigarette,  drop  a  reference  to  the  "little  lady,"  and  say  he  was  happy  to  see  the  firm  employing  some  coloured  folks  in  important  positions.  Any  of  those  acts  would  earn  a  swift  reprimand,  and  together  they  might  get  him  fired.  When  she  went  into  the  city  to  shop,  the  wife  would  put  on  a  nice  suit,  hat,  and  possibly  gloves.  She  would  not  understand  why  people  stared,  and  mocked.  And  when  the  whole  family  sat  down  after  dinner  and  turned  on  the  television,  they  would  not  understand  how  pornography  from  some  sleazy,  blank-fronted  "Adults  Only"  kiosk  had  gotten  on  their  set.  Were  they  able,  our  1950s  family  would  head  back  to  the  1950s  as  fast  as  they  could,  with  a  gripping  horror  story  to  tell.  Their  story  would  be  of  a  nation  that  had  decayed  and  degenerated  at  a  fantastic  pace,  moving  in  less  than  a  half  a  century  from  the  greatest  countries  on  earth  to  Third  World  nations,  overrun  by  crime,  noise,  drugs  and  dirt.  The  fall  of  Rome  was  graceful  by  comparison.  Why  did  it  happen?  Over  the  last  fifty  years,  Western  Europe  has  been  conquered  by  the  same  force  that  earlier  took  over  Russia,  China,  Germany  and  Italy.  That  force  is  ideology.  Here,  as  elsewhere,  ideology  has  inflicted  enormous  damage  on  the  traditional  culture  it  came  to  dominate,  fracturing  it  everywhere  and  sweeping  much  of  it  away.  In  its  place  came  fear,  and  ruin.  Russia  will  take  a  generation  or  more  to  recover  from  Communism,  if  it  ever  can.  The  ideology  that  has  taken  over  Western  Europe  goes  most  commonly  by  the  name  of  "Political  Correctness."  Some  people  see  it  as  a  joke.  It  is  not.  It  is  deadly  serious.  It  seeks  to  alter  virtually  all  the  rules,  formal  and  informal,  that  govern  relations  among  people  and  institutions.  It  wants  to  change  behaviour,  thought,  even  the  words  we  use.  To  a  significant  extent,  it  already  has.  Whoever  or  whatever  controls  language  also  controls  thought.  Who  dares  to  speak  of  "ladies"  now?  Just  what  is  "Political  Correctness?"  Political  Correctness  is  in  fact  cultural  Marxism  (Cultural  Communism)  -  Marxism  translated  from  economic  into  cultural  terms.  The  effort  to  translate  Marxism  from  economics  into  culture  did  not  begin  with  the  student  rebellion  of  the  1960s.  It  goes  back  at  least  to  the  1920s  and  the  writings  of  the  Italian  Communist  Antonio  Gramsci.  In  1923,  in  Germany,  a  group  of  Marxists  founded  an  institute  devoted  to  making  the  transition,  the  Institute  of  Social  Research  (later  known  as  the  Frankfurt  School).  One  of  its  founders,  George  Lukacs,  stated  its  purpose  as  answering  the  question,  "Who  shall  save  us  from  Western  Civilisation?"  The  Frankfurt  School  gained  profound  influence  in  European  and  American  universities  after  many  of  its  leading  lights  fled  and  spread  all  over  Europe  and  even  to  the  United  States  in  the  1930s  to  escape  National  Socialism  in  Germany.  In  Western  Europe  it  gained  influence  in  universities  from  1945.  The  Frankfurt  School  blended  Marx  with  Freud,  and  later  influences  (some  Fascist  as  well  as  Marxist)  added  linguistics  to  create  "Critical  Theory"  and  "deconstruction."  These  in  turn  greatly  influenced  education  theory,  and  through  institutions  of  higher  education  gave  birth  to  what  we  now  call  "Political  Correctness."  The  lineage  is  clear,  and  it  is  traceable  right  back  to  Karl  Marx.  The  parallels  between  the  old,  economic  Marxism  and  cultural  Marxism  are  evident.  Cultural  Marxism,  or  Political  Correctness,  shares  with  classical  Marxism  the  vision  of  a  "classless  society,"  i.e.,  a  society  not  merely  of  equal  opportunity,  but  equal  condition.  Since  that  vision  contradicts  human  nature  -  because  people  are  different,  they  end  up  unequal,  regardless  of  the  starting  point  -  society  will  not  accord  with  it  unless  forced.  So,  under  both  variants  of  Marxism,  it  is  forced.  This  is  the  first  major  parallel  between  classical  and  cultural  Marxism:  both  are  totalitarian  ideologies.  The  totalitarian  nature  of  Political  Correctness  can  be  seen  on  campuses  where  "PC"  has  taken  over  the  college:  freedom  of  speech,  of  the  press,  and  even  of  thought  are  all  eliminated.  The  second  major  parallel  is  that  both  classical,  economic  Marxism  and  cultural  Marxism  have  single-factor  explanations  of  history.  Classical  Marxism  argues  that  all  of  history  was  determined  by  ownership  of  the  means  of  production.  Cultural  Marxism  says  that  history  is  wholly  explained  by  which  groups  -  defined  by  sex,  race,  religion  and  sexual  normality  or  abnormality  -  have  power  over  which  other  groups.  The  third  parallel  is  that  both  varieties  of  Marxism  declare  certain  groups  virtuous  and  others  evil  a  priori,  that  is,  without  regard  for  the  actual  behaviour  of  individuals.  Classical  Marxism  defines  workers  and  peasants  as  virtuous  and  the  bourgeoisie  (the  middle  class)  and  other  owners  of  capital  as  evil.  Cultural  Marxism  defines  all  minorities,  what  they  see  as  the  victims;  Muslims,  Feminist  women,  homosexuals  and  some  additional  minority  groups  as  virtuous  and  they  view  ethnic  Christian  European  men  as  evil.  (Cultural  Marxism  does  not  recognise  the  existence  of  non-Feminist  women,  and  defines  Muslims,  Asians  and  Africans  who  reject  Politi</t>
+  </si>
+  <si>
+    <t>INDUSTRIAL SOCIETY AND ITS FUTURE Introduction 1. The Industrial Revolution and its consequences have been a disaster for the     human race. They have greatly increased the life-expectancy of those of us     who live in “advanced” countries, but they have destabilized society, have     made life unfulfilling, have subjected human beings to indignities, have led     to widespread psychological suffering (in the Third World to physical     suffering as well) and have inflicted severe damage on the natural world. The     continued development of technology will worsen the situation. It will     certainly subject human beings to greater indignities and inflict greater     damage on the natural world, it will probably lead to greater social     disruption and psychological suffering, and it may lead to increased physical     suffering even in “advanced” countries. 2. The industrial-technological system may survive or it may break down. If it     survives, it MAY eventually achieve a low level of physical and psychological     suffering, but only after passing through a long and very painful period of     adjustment and only at the cost of permanently reducing human beings and many     other living organisms to engineered products and mere cogs in the social     machine. Furthermore, if the system survives, the consequences will be     inevitable: There is no way of reforming or modifying the system so as to     prevent it from depriving people of dignity and autonomy. 3. If the system breaks down the consequences will still be very painful. But     the bigger the system grows the more disastrous the results of its breakdown     will be, so if it is to break down it had best break down sooner rather than     later. 4. We therefore advocate a revolution against the industrial system. This     revolution may or may not make use of violence; it may be sudden or it may be     a relatively gradual process spanning a few decades. We can’t predict any of     that. But we do outline in a very general way the measures that those who     hate the industrial system should take in order to prepare the way for     a revolution against that form of society. This is not to be a POLITICAL     revolution. Its object will be to overthrow not governments but the economic     and technological basis of the present society. 5. In this article we give attention to only some of the negative developments     that have grown out of the industrial-technological system. Other such     developments we mention only briefly or ignore altogether. This does not mean     that we regard these other developments as unimportant. For practical reasons     we have to confine our discussion to areas that have received insufficient     public attention or in which we have something new to say. For example, since     there are well-developed environmental and wilderness movements, we have     written very little about environmental degradation or the destruction of     wild nature, even though we consider these to be highly important. THE PSYCHOLOGY OF MODERN LEFTISM 6. Almost everyone will agree that we live in a deeply troubled society. One of     the most widespread manifestations of the craziness of our world is leftism,     so a discussion of the psychology of leftism can serve as an introduction to     the discussion of the problems of modern society in general. 7. But what is leftism? During the first half of the 20th century leftism could     have been practically identified with socialism. Today the movement is     fragmented and it is not clear who can properly be called a leftist. When we     speak of leftists in this article we have in mind mainly socialists,     collectivists, “politically correct” types, feminists, gay and disability     activists, animal rights activists and the like. But not everyone who is     associated with one of these movements is a leftist. What we are trying to     get at in discussing leftism is not so much movement or an ideology as     a psychological type, or rather a collection of related types. Thus, what we     mean by “leftism” will emerge more clearly in the course of our discussion of     leftist psychology. (Also, see paragraphs 227-230.) 8. Even so, our conception of leftism will remain a good deal less clear than we     would wish, but there doesn’t seem to be any remedy for this. All we are     trying to do here is indicate in a rough and approximate way the two     psychological tendencies that we believe are the main driving force of modern     leftism. We by no means claim to be telling the WHOLE truth about leftist     psychology. Also, our discussion is meant to apply to modern leftism only. We     leave open the question of the extent to which our discussion could be     applied to the leftists of the 19th and early 20th centuries. 9. The two psychological tendencies that underlie modern leftism we call     “feelings of inferiority” and “oversocialization.” Feelings of inferiority     are characteristic of modern leftism as a whole, while oversocialization is     characteristic only of a certain segment of modern leftism; but this segment     is highly influential. FEELINGS OF INFERIORITY 10. By “feelings of inferiority” we mean not only inferiority feelings in the      strict sense but a whole spectrum of related traits; low self-esteem,      feelings of powerlessness, depressive tendencies, defeatism, guilt, self-      hatred, etc. We argue that modern leftists tend to have some such feelings      (possibly more or less repressed) and that these feelings are decisive in      determining the direction of modern leftism. 11. When someone interprets as derogatory almost anything that is said about him      (or about groups with whom he identifies) we conclude that he has      inferiority feelings or low self-esteem. This tendency is pronounced among      minority rights activists, whether or not they belong to the minority groups      whose rights they defend. They are hypersensitive about the words used to      designate minorities and about anything that is said concerning minorities.      The terms “negro,” “oriental,” “handicapped” or “chick” for an African, an      Asian, a disabled person or a woman originally had no derogatory      connotation. “Broad” and “chick” were merely the feminine equivalents of      “guy,” “dude” or “fellow.” The negative connotations have been attached to      these terms by the activists themselves. Some animal rights activists have      gone so far as to reject the word “pet” and insist on its replacement by      “animal companion.” Leftish anthropologists go to great lengths to avoid      saying anything about primitive peoples that could conceivably be      interpreted as negative. They want to replace the world “primitive” by      “nonliterate.” They seem almost paranoid about anything that might suggest      that any primitive culture is inferior to our own. (We do not mean to imply      that primitive cultures ARE inferior to ours. We merely point out the      hypersensitivity of leftish anthropologists.) 12. Those who are most sensitive about “politically incorrect” terminology are      not the average black ghetto- dweller, Asian immigrant, abused woman or      disabled person, but a minority of activists, many of whom do not even      belong to any “oppressed” group but come from privileged strata of society.      Political correctness has its stronghold among university professors, who      have secure employment with comfortable salaries, and the majority of whom      are heterosexual white males from middle- to upper-middle-class families. 13. Many leftists have an intense identification with the problems of groups      that have an image of being weak (women), defeated (American Indians),      repellent (homosexuals) or otherwise inferior. The leftists themselves feel      that these groups are inferior. They would never admit to themselves that      they have such feelings, but it is precisely because they do see these      groups as inferior that they identify with their problems. (We do not mean      to suggest that women, Indians, etc. ARE inferior; we are only making      a point about leftist psychology.) 14. Feminists are desperately anxious to prove that women are as strong and as      capable as men. Clearly they are nagged by a fear that women may NOT be as      strong and as capable as men. 15. Leftists tend to hate anything that has an image of being strong, good and      successful. They hate America, they hate Western civilization, they hate      white males, they hate rationality. The reasons that leftists give for      hating the West, etc. clearly do not correspond with their real motives.      They SAY they hate the West because it is warlike, imperialistic, sexist,      ethnocentric and so forth, but where these same faults appear in socialist      countries or in primitive cultures, the leftist finds excuses for them, or      at best he GRUDGINGLY admits that they exist; whereas he ENTHUSIASTICALLY      points out (and often greatly exaggerates) these faults where they appear in      Western civilization. Thus it is clear that these faults are not the      leftist’s real motive for hating America and the West. He hates America and      the West because they are strong and successful. 16. Words like “self-confidence,” “self-reliance,” “initiative,” “enterprise,”      “optimism,” etc., play little role in the liberal and leftist vocabulary.      The leftist is anti-individualistic, pro-collectivist. He wants society to      solve everyone’s problems for them, satisfy everyone’s needs for them, take      care of them. He is not the sort of person who has an inner sense of      confidence in his ability to solve his own problems and satisfy his own      needs. The leftist is antagonistic to the concept of competition because,      deep inside, he feels like a loser. 17. Art forms that appeal to modern leftish intellectuals tend to focus on      sordidness, defeat and despair, or else they take an orgiastic tone,      throwing off rational control as if there were no hope of accomplishing      anything through rational calculation and all that was left was to immerse      oneself in the sensations of the moment. 18. Modern leftish philosophers tend to dismiss reason, science, objective      reality and to insist that everything is culturally relative. It is true      that one can ask serious questions about the foundations of scientific      knowledge and about how, if at all, the concept of objective reality can be      defined. But it is obvious that modern leftish philosophers are not simply      cool-headed logicians systematically analyzing the foundations of knowledge.      They are deeply involved emotionally in their attack on truth and reality.      They attack these concepts because of their own psychological needs. For one      thing, their attack is an outlet for hostility, and, to the extent that it      is successful, it satisfies the drive for power. More importantly, the      leftist hates science and rationality because they classify certain beliefs      as true (i.e., successful, superior) and other beliefs as false (i.e.,      failed, inferior). The leftist’s feelings of inferiority run so deep that he      cannot tolerate any classification of some things as successful or superior      and other things as failed or inferior. This also underlies the rejection by      many leftists of the concept of mental illness and of the utility of IQ      tests. Leftists are antagonistic to genetic explanations of human abilities      or behavior because such explanations tend to make some persons appear      superior or inferior to others. Leftists prefer to give society the credit      or blame for an individual’s ability or lack of it. Thus if a person is      “inferior” it is not his fault, but society’s, because he has not been      brought up properly. 19. The leftist is not typically the kind of person whose feelings of      inferiority make him a braggart, an egotist, a bully, a self-promoter,      a ruthless competitor. This kind of person has not wholly lost faith in      himself. He has a deficit in his sense of power and self-worth, but he can      still conceive of himself as having the capacity to be strong, and his      efforts to make himself strong produce his unpleasant behavior. [1] But the      leftist is too far gone for that. His feelings of inferiority are so      ingrained that he cannot conceive of himself as individually strong and      valuable. Hence the collectivism of the leftist. He can feel strong only as      a member of a large organization or a mass movement with which he identifies      himself. 20. Notice the masochistic tendency of leftist tactics. Leftists protest by      lying down in front of vehicles, they intentionally provoke police or      racists to abuse them, etc. These tactics may often be effective, but many      leftists use them not as a means to an end but because they PREFER      masochistic tactics. Self-hatred is a leftist trait. 21. Leftists may claim that their activism is motivated by compassion or by      moral principles, and moral principle does play a role for the leftist of      the oversocialized type. But compassion and moral principle cannot be the      main motives for leftist activism. Hostility is too prominent a component of      leftist behavior; so is the drive for power. Moreover, much leftist behavior      is not rationally calculated to be of benefit to the people whom the      leftists claim to be trying to help. For example, if one believes that      affirmative action is good for black people, does it make sense to demand      affirmative action in hostile or dogmatic terms? Obviously it would be more      productive to take a diplomatic and conciliatory approach that would make at      least verbal and symbolic concessions to white people who think that      affirmative action discriminates against them. But leftist activists do not      take such an approach because it would not satisfy their emotional needs.      Helping black people is not their real goal. Instead, race problems serve as      an excuse for them to express their own hostility and frustrated need for      power. In doing so they actually harm black people, because the activists’      hostile attitude toward the white majority tends to intensify race hatred. 22. If our society had no social problems at all, the leftists would have to      INVENT problems in order to provide themselves with an excuse for making      a fuss. 23. We emphasize that the foregoing does not pretend to be an accurate      description of everyone who might be considered a leftist. It is only      a rough indication of a general tendency of leftism. OVERSOCIALIZATION 24. Psychologists use the term “socialization” to designate the process by which      children are trained to think and act as society demands. A person is said      to be well socialized if he believes in and obeys the moral code of his      society and fits in well as a functioning part of that society. It may seem      senseless to say that many leftists are oversocialized, since the leftist is      perceived as a rebel. Nevertheless, the position can be defended. Many      leftists are not such rebels as they seem. 25. The moral code of our society is so demanding that no one can think, feel      and act in a completely moral way. For example, we are not supposed to hate      anyone, yet almost everyone hates somebody at some time or other, whether he      admits it to himself or not. Some people are so highly socialized that the      attempt to think, feel and act morally imposes a severe burden on them. In      order to avoid feelings of guilt, they continually have to deceive      themselves about their own motives and find moral explanations for feelings      and actions that in reality have a non-moral origin. We use the term      “oversocialized” to describe such people. [2] 26. Oversocialization can lead to low self-esteem, a sense of powerlessness,      defeatism, guilt, etc. One of the most important means by which our society      socializes children is by making them feel ashamed of behavior or speech      that is contrary to society’s expectations. If this is overdone, or if      a particular child is especially susceptible to such feelings, he ends by      feeling ashamed of HIMSELF. Moreover the thought and the behavior of the      oversocialized person are more restricted by society’s expectations than are      those of the lightly socialized person. The majority of people engage in      a significant amount of naughty behavior. They lie, they commit petty      thefts, they break traffic laws, they goof off at work, they hate someone,      they say spiteful things or they use some underhanded trick to get ahead of      the other guy. The oversocialized person cannot do these things, or if he      does do them he generates in himself a sense of shame and self-hatred. The      oversocialized person cannot even experience, without guilt, thoughts or      feelings that are contrary to the accepted morality; he cannot think      “unclean” thoughts. And socialization is not just a matter of morality; we      are socialized to conform to many norms of behavior that do not fall under      the heading of morality. Thus the oversocialized person is kept on      a psychological leash and spends his life running on rails that society has      laid down for him. In many oversocialized people this results in a sense of      constraint and powerlessness that can be a severe hardship. We suggest that      oversocialization is among the more serious cruelties that human beings      inflict on one another. 27. We argue that a very important and influential segment of the modern left is      oversocialized and that their oversocialization is of great importance in      determining the direction of modern leftism. Leftists of the oversocialized      type tend to be intellectuals or members of the upper-middle class. Notice      that university intellectuals [3] constitute the most highly socialized      segment of our society and also the most left-wing segment. 28. The leftist of the oversocialized type tries to get off his psychological      leash and assert his autonomy by rebelling. But usually he is not strong      enough to rebel against the most basic values of society. Generally      speaking, the goals of today’s leftists are NOT in conflict with the      accepted morality. On the contrary, the left takes an accepted moral      principle, adopts it as its own, and then accuses mainstream society of      violating that principle. Examples: racial equality, equality of the sexes,      helping poor people, peace as opposed to war, nonviolence generally, freedom      of expression, kindness to animals. More fundamentally, the duty of the      individual to serve society and the duty of society to take care of the      individual. All these have been deeply rooted values of our society (or at      least of its middle and upper classes [4] for a long time. These values are      explicitly or implicitly expressed or presupposed in most of the material      presented to us by the mainstream communications media and the educational      system. Leftists, especially those of the oversocialized type, usually do      not rebel against these principles but justify their hostility to society by      claiming (with some degree of truth) that society is not living up to these      principles. 29. Here is an illustration of the way in which the oversocialized leftist shows      his real attachment to the conventional attitudes of our society while      pretending to be in rebellion against it. Many leftists push for affirmative      action, for moving black people into high-prestige jobs, for improved      education in black schools and more money for such schools; the way of life      of the black “underclass” they regard as a social disgrace. They want to      integrate the black man into the system, make him a business executive,      a lawyer, a scientist just like upper-middle-class white people. The      leftists will reply that the last thing they want is to make the black man      into a copy of the white man; instead, they want to preserve African      American culture. But in what does this preservation of African American      culture consist? It can hardly consist in anything more than eating      black-style food, listening to black-style music, wearing black-style      clothing and going to a black- style church or mosque. In other words, it      can express itself only in superficial matters. In all ESSENTIAL respects      most leftists of the oversocialized type want to make the black man conform      to white, middle-class ideals. They want to make him study technical      subjects, become an executive or a scientist, spend his life climbing the      status ladder to prove that black people are as good as white. They want to      make black fathers “responsible,” they want black gangs to become      nonviolent, etc. But these are exactly the values of the      industrial-technological system. The system couldn’t care less what kind of      music a man listens to, what kind of clothes he wears or what religion he      believes in as long as he studies in school, holds a respectable job, climbs      the status ladder, is a “responsible” parent, is nonviolent and so forth. In      effect, however much he may deny it, the oversocialized leftist wants to      integrate the black man into the system and make him adopt its values. 30. We certainly do not claim that leftists, even of the oversocialized type,      NEVER rebel against the fundamental values of our society. Clearly they      sometimes do. Some oversocialized leftists have gone so far as to rebel      against one of modern society’s most important principles by engaging in      physical violence. By their own account, violence is for them a form of      “liberation.” In other words, by committing violence they break through the      psychological restraints that have been trained into them. Because they are      oversocialized these restraints have been more confining for them than for      others; hence their need to break free of them. But they usually justify      their rebellion in terms of mainstream values. If they engage in violence      they claim to be fighting against racism or the like. 31. We realize that many objections could be raised to the foregoing thumbnail      sketch of leftist psychology. The real situation is complex, and anything      like a complete description of it would take several volumes even if the      necessary data were available. We claim only to have indicated very roughly      the two most important tendencies in the psychology of modern leftism. 32. The problems of the leftist are indicative of the problems of our society as      a whole. Low self-esteem, depressive tendencies and defeatism are not      restricted to the left. Though they are especially noticeable in the left,      they are widespread in our society. And today’s society tries to socialize      us to a greater extent than any previous society. We are even told by      experts how to eat, how to exercise, how to make love, how to raise our kids      and so forth. THE POWER PROCESS 33. Human beings have a need (probably based in biology) for something that we      will call the “power process.” This is closely related to the need for power      (which is widely recognized) but is not quite the same thing. The power      process has four elements. The three most clear-cut of these we call goal,      effort and attainment of goal. (Everyone needs to have goals whose      attainment requires effort, and needs to succeed in attaining at least some      of his goals.) The fourth element is more difficult to define and may not be      necessary for everyone. We call it autonomy and will discuss it later      (paragraphs 42-44). 34. Consider the hypothetical case of a man who can have anything he wants just      by wishing for it. Such a man has power, but he will develop serious      psychological problems. At first he will have a lot of fun, but by and by he      will become acutely bored and demoralized. Eventually he may become      clinically depressed. History shows that leisured aristocracies tend to      become decadent. This is not true of fighting aristocracies that have to      struggle to maintain their power. But leisured, secure aristocracies that      have no need to exert themselves usually become bored, hedonistic and      demoralized, even though they have power. This shows that power is not      enough. One must have goals toward which to exercise one’s power. 35. Everyone has goals; if nothing else, to obtain the physical necessities of      life: food, water and whatever clothing and shelter are made necessary by      the climate. But the leisured aristocrat obtains these things without      effort. Hence his boredom and demoralization. 36. Nonattainment of important goals results in death if the goals are physical      necessities, and in frustration if nonattainment of the goals is compatible      with survival. Consistent failure to attain goals throughout life results in      defeatism, low self-esteem or depression. 37, Thus, in order to avoid serious psychological problems, a human being needs      goals whose attainment requires effort, and he must have a reasonable rate      of success in attaining his goals. SURROGATE ACTIVITIES 38. But not every leisured aristocrat becomes bored and demoralized. For      example, the emperor Hirohito, instead of sinking into decadent hedonism,      devoted himself to marine biology, a field in which he became distinguished.      When people do not have to exert themselves to satisfy their physical needs      they often set up artificial goals for themselves. In many cases they then      pursue these goals with the same energy and emotional involvement that they      otherwise would have put into the search for physical necessities. Thus the      aristocrats of the Roman Empire had their literary pretensions; many      European aristocrats a few centuries ago invested tremendous time and energy      in hunting, though they certainly didn’t need the meat; other aristocracies      have competed for status through elaborate displays of wealth; and a few      aristocrats, like Hirohito, have turned to science. 39. We use the term “surrogate activity” to designate an activity that is      directed toward an artificial goal that people set up for themselves merely      in order to have some goal to work toward, or let us say, merely for the      sake of the “fulfillment” that they get from pursuing the goal. Here is      a rule of thumb for the identification of surrogate activities. Given      a person who devotes much time and energy to the pursuit of goal X, ask      yourself this: If he had to devote most of his time and energy to satisfying      his biological needs, and if that effort required him to use his physical      and mental faculties in a varied and interesting way, would he feel      seriously deprived because he did not attain goal X? If the answer is no,      then the person’s pursuit of goal X is a surrogate activity. Hirohito’s      studies in marine biology clearly constituted a surrogate activity, since it      is pretty certain that if Hirohito had had to spend his time working at      interesting non-scientific tasks in order to obtain the necessities of life,      he would not have felt deprived because he didn’t know all about the anatomy      and life-cycles of marine animals. On the other hand the pursuit of sex and      love (for example) is not a surrogate activity, because most people, even if      their existence were otherwise satisfactory, would feel deprived if they      passed their lives without ever having a relationship with a member of the      opposite sex. (But pursuit of an excessive amount of sex, more than one      really needs, can be a surrogate activity.) 40. In modern industrial society only minimal effort is necessary to satisfy      one’s physical needs. It is enough to go through a training program to      acquire some petty technical skill, then come to work on time and exert the      very modest effort needed to hold a job. The only requirements are      a moderate amount of intelligence and, most of all, simple OBEDIENCE. If one      has those, society takes care of one from cradle to grave. (Yes, there is an      underclass that cannot take the physical necessities for granted, but we are      speaking here of mainstream society.) Thus it is not surprising that modern      society is full of surrogate activities. These include scientific work,      athletic achievement, humanitarian work, artistic and literary creation,      climbing the corporate ladder, acquisition of money and material goods far      beyond the point at which they cease to give any additional physical      satisfaction, and social activism when it addresses issues that are not      important for the activist personally, as in the case of white activists who      work for the rights of nonwhite minorities. These are not always PURE      surrogate activities, since for many people they may be motivated in part by      needs other than the need to have some goal to pursue. Scientific work may      be motivated in part by a drive for prestige, artistic creation by a need to      express feelings, militant social activism by hostility. But for most people      who pursue them, these activities are in large part surrogate activities.      For example, the majority of scientists will probably agree that the      “fulfillment” they get from their work is more important than the money and      prestige they earn. 41. For many if not most people, surrogate activities are less satisfying than      the pursuit of real goals (that is, goals that people would want to attain      even if their need for the power process were already fulfilled). One      indication of this is the fact that, in many or most cases, people who are      deeply involved in surrogate activities are never satisfied, never at rest.      Thus the money-maker constantly strives for more and more wealth. The      scientist no sooner solves one problem than he moves on to the next. The      long-distance runner drives himself to run always farther and faster. Many      people who pursue surrogate activities will say that they get far more      fulfillment from these activities than they do from the “mundane” business      of satisfying their biological needs, but that is because in our society the      effort needed to satisfy the biological needs has been reduced to      triviality. More importantly, in our society people do not satisfy their      biological needs AUTONOMOUSLY but by functioning as parts of an immense      social machine. In contrast, people generally have a great deal of autonomy      in pursuing their surrogate activities. AUTONOMY 42. Autonomy as a part of the power process may not be necessary for every      individual. But most people need a greater or lesser degree of autonomy in      working toward their goals. Their efforts must be undertaken on their own      initiative and must be under their own direction and control. Yet most      people do not have to exert this initiative, direction and control as single      individuals. It is usually enough to act as a member of a SMALL group. Thus      if half a dozen people discuss a goal among themselves and make a successful      joint effort to attain that goal, their need for the power process will be      served. But if they work under rigid orders handed down from above that      leave them no room for autonomous decision and initiative, then their need      for the power process will not be served. The same is true when decisions      are made on a collective basis if the group making the collective decision      is so large that the role of each individual is insignificant. [5] 43. It is true that some individuals seem to have little need for autonomy.      Either their drive for power is weak or they satisfy it by identifying      themselves with some powerful organization to which they belong. And then      there are unthinking, animal types who seem to be satisfied with a purely      physical sense of power (the good combat soldier, who gets his sense of      power by developing fighting skills that he is quite content to use in blind      obedience to his superiors). 44. But for most people it</t>
+  </si>
+  <si>
     <t>ATTACK INFORMATION Event: Jokela High School Massacre. Targets: Jokelan Lukio (High School Of Jokela), students and faculty, society, humanity, human race. Date: 11/7/2007. Attack Type: Mass murder, political terrorism (altough I choosed the school as target, my motives for the attack are political and much much deeper and therefore I don’t want this to be called only as “school shooting”). Location: Jokela, Tuusula, Finland. Perpetrator’s name: Pekka-Eric Auvinen (aka NaturalSelector89, Natural Selector, Sturmgeist89 and Sturmgeist). I also use pseydonym Eric von Auffoin internationally. Weapons: Semi-automatic .22 Sig Sauer Mosquito pistol. What do I hate / What I don’t like? Equality, tolerance, human rights, political correctness, hypocrisy, ignorance, enslaving religions and ideologies, antidepressants, TV soap operas &amp; drama shows, rap -music, mass media, censorship, political populists, religious fanatics, moral majority, totalitarianism, consumerism, democracy, pacifism, state mafia, alcholohics, TV commercials, human race. What do I love / what do I like? Existentialism, self-awareness, freedom, justice, truth, moral &amp; political philosophy, personal &amp; social psychology, evolution science, political incorrectness, guns, shooting, BDSM, computers, internet, aggressive electronic and industrial rock &amp; metal music, violent movies, , FPS –computer games, sarcasm, irony, black humour, macabre artm mass &amp; serial killer cases, natural disasters, eugenics Natural Selector’s Manifesto How Did Natural Selection Turn Into Idiocratic Selection? Today the process of natural selection is totally misguided. It has reversed. Human race has been devolving very long time for now. Retarded and stupid , weak-minded people are reproducing more and faster than the intelligent, strong-minded people. Laws protect the retarded majority which selects the leaders of society. Modern human race has not only betrayed its ancestors, but the future generations too. Homo Sapiens, HAH! It is more like a Homo Idioticus to me! When I look at people I see every day in society, school and everywhere... I can’t say I belong to same race as the lousy, miserable, arrogant, selfish human race! No! I have evolved one step above! Naturality has been discriminated through religions, ideologies, laws and other mass delusion systems. Individual, who is going through his/hers natural power process and trying to live naturally, but is being told that the way he acts or thinks is wrong and stupid, will usually have some reactions which might be considered as "psychological disorders" by the establishment. In reality they are just natural reactions to the disruption of natural power process. They will have some of the following (depending on individual's personality): feelings of inferiority / superiority, hostility, aggression, frustration, depression, self-hatred / hatred towards other people, suicidal / homicidal thought etc... and it is completely normal. Humans are just a species among other animals and world does not exist only for humans. Death and killing is not a tragedy, it happens in nature all the time between all species. Not all human lives are important or worth saving. Only superior (intelligent, self-aware, strong-minded) individuals should survive while inferior (stupid, retarded, weak-minded masses) should perish. There is also another solution to the problem: stupid people as slaves and intelligent people as free. What I mean is that they who have free minds, are capable of intelligent existential and philosophical thinking and know what justice is, should be free and rulers... and the robotic masses, they can be slaves since they do not mind it now either and because their minds are on so retarded level. The gangsters that now rule societies, would of course get what they deserve. Of course there is a final solution too: death of entire human race. It would solve every problem of humanity. The faster human race is wiped out from this planet, the better... no one should be left alive. I have no mercy for the scum of earth, the pathetic human race. Collective Deindividualization: Totalitarianism &amp; Delusions Of Democracy Collective deindividualization is a phenomenon where individual will be trained as part of the mindless herd controlled by state, corporation, church or some other organization, group, ideology, religion or mass delusion system and adopt it's rules, morality and codes of conduct. This phenomenon has been familiar in all despotic, authoritarian, totalitarian, monarchist, communist, socialist, nazi, fascist and religious societies troughout history. Also, the modern western democratic republics have the same phenomenon. It is just done so that people will think they are free and don't realize they are being enslaved. Majority of people in society are weak-minded and ignorant retards, masses that act like programmed robots and accept voluntarily slavery. But not me! I am self-aware and realize what is going on in society! I have a free mind! And I choose to be free rather than live like a robot or slave. You can say I have a “god complex”, sure... then you have a “group complex”! Compared to you retarded masses, I am actually godlike. Totalitarian governments rule people through education system, consumerism, mass media, monopoly on the legitimate use of physical force (police, military) and laws discriminating people who think differently than the majority. Democracy... you think democracy means freedom and justice? You are wrong. Democracy is a dictatorship of the moral majority... and the majority is manipulated and ruled by the state mafia. Modern western democracy has nothing to do with freedom or justice; it is totalitarian and corrupted system. Laws are made over the heads of the people and people are being brainwashed to support the system and connected to the institutional structures immediately after their birth. Societies are being ruled by manipulative and charismatic politicians who only care about the interests of majority, and who do not base their decisions on reason but emotions and feelings of the masses. These masses let the authorities of state to make all the important decisions for them. The masses will get an education, they study, get a job, go to work and vote in elections. They think they are free and don’t criticise or question the system. They have become robots. It is like a constructed mechanism in mind, that leaves little choice for an individual to think, talk and act independently. Three Kinds Of Humans There are three kinds of human personality types in this world: 1) individualistic human (3% of the world population) 2) manipulative human (3% of the world population) 3) mass human (94% of the world population) #1 &amp; #2 type of personalities are intelligent, creative and self-aware. They have chosen bit different paths paths. #3 type of personalities are less intelligent and less creative, weak-minded people controlled by #2 type of personalities. The percentages are only estimations though but are based on Gaussian distribution and history of human race and how humans have organized into societies. And this is the way it has always been ever since humans started to organize into communities. Another way how to divide people is bit different but is based on the same facts, human nature and history. The division is based on the level of intelligence and quality of mentality: 1) intelligent (3% of the world population) 2) slightly retarded, so called “normal people” or “robots” (94% of the world population) 3) highly retarded, “vegetables” (3% of the world population) Total War Against Humanity Hate, Im so full of it and I love it. That is one thing I really love. Some time ago, I used to believe in humanity and I wanted to live a long and happy life... but then I woke up. I started to think deeper and realized things. But it was not easy to become existential... knowing as much as I know has made me unhappy, frustrated and angry. I just can’t be happy in the society or the reality I live. Due to long process of existential thinking, observing the society I live and some other things happened in my life... I have come to the point where I feel nothing but hate against humanity and human race. Life is just a meaningless coincidence... result of long process of evolution and many several factors, causes and effects. However, life is also something that an individual wants and determines it to be. And I'm the dictator and god of my own life. And me, I have chosen my way. I am prepared to fight and die for my cause. I, as a natural selector, will eliminate all who I see unfit, disgraces of human race and failures of natural selection. You might ask yourselves, why did I do this and what do I want. Well, most of you are too arrogant and closed-minded to understand... You will proprably say me that I am “insane”, “crazy”, “psychopath”, “criminal” or crap like that. No, the truth is that I am just an animl, a human, an individual, a dissident. I have had enough. I don’t want to be part of this fucked up society. Like some other wise people have said in the past, human race is not worth fighting for or saving... only worth killing. But... When my enemies will run and hide in fear when mentioning my name... When the gangsters of the corrupted governments have been shot in the streets... When the rule of idioracy and the democratic system has been replaced with justice... When intelligent people are finally free and rule the society instead of the idiocratic rule of majority... In that great day of deliverance, you will know what I want. Long live the revolution... revolution against the system, which enslaves not only the majority of weak-minded masses but also the small minority of strong-minded and intelligent individuals! If we want to live in a different world, we must act. We must rise against the enslaving, corrupted and totalitarian regimes and overthrow the tyrants, gangsters and the rule of idiocracy. I can’t alone change much but hopefully my actions will inspire all the intelligent people of the world and start some sort of revolution against the current systems. The system discriminating naturality and justice, is my enemy. The people living in the world of delusion and supporting this system are my enemies. I am ready to die for a cause I know is right, just and true... even if I would lose or the battle would be only remembered as evil... I will rather fight and die than live a long and unhappy life. And remember that this is my war, my ideas and my plans. Don’t blame anyone else for my actions than myself. Don’t blame my parents or my friends. I told nobody about my plans and I always kept them inside my mind only. Don’t blame the movies I see, the music I hear, the games I play or the books I read. No, they had nothing to do with this. This is my war: one man war against humanity, governments and weak-minded masses of the world! No mercy for the scum of the earth! HUMANITY IS OVERRATED! It's time to put NATURAL SELECTION &amp; SURVIVAL OF THE FITTEST back on tracks! Justice renders to everyone his due. - Pekka-Eric Auvinen (aka NaturalSelector89, Natural Selector, Sturmgeist89 and Sturmgeist). I also use pseydonym Eric von Auffoin internationally.</t>
   </si>
   <si>
@@ -44,6 +50,12 @@
   </si>
   <si>
     <t>Valery Fabrikant</t>
+  </si>
+  <si>
+    <t>Anders Behring Breivik</t>
+  </si>
+  <si>
+    <t>Theodore Kaczynski</t>
   </si>
   <si>
     <t>Pekka Eric Auvinen</t>
@@ -407,13 +419,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="100.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -441,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -455,7 +467,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -469,7 +481,35 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
